--- a/tests/integration_workspace/dashboard_full_pipeline/output/_FULL_RESULT_FOR_STOCK.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/_FULL_RESULT_FOR_STOCK.xlsx
@@ -489,7 +489,11 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SVO SHAMPUN APPLE 1 л</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>MATCH</t>
@@ -527,7 +531,11 @@
           <t>SKU-LIME</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SVO SHAMPUN LIME 1 л</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>MATCH</t>
